--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_isapre_a_2021_tarapaca.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_isapre_a_2021_tarapaca.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:31</t>
+    <t xml:space="preserve">2026-09-24 01:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -941,7 +941,7 @@
         <v>-0.42</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>-0.2</v>
@@ -964,7 +964,7 @@
         <v>-0.35</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>-0.53</v>
@@ -987,7 +987,7 @@
         <v>-0.27</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>-0.06</v>
@@ -1007,13 +1007,13 @@
         <v>6</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="23">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_isapre_a_2021_tarapaca.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_isapre_a_2021_tarapaca.xlsx
@@ -123,7 +123,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:21</t>
+    <t xml:space="preserve">2026-10-01 23:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_isapre_a_2021_tarapaca.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_isapre_a_2021_tarapaca.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:21</t>
+    <t xml:space="preserve">2026-10-05 19:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
